--- a/storage/app/public/vocabs/analogue/1.4/analogue_1-4.xlsx
+++ b/storage/app/public/vocabs/analogue/1.4/analogue_1-4.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1356">
   <si>
     <t>synonyms</t>
   </si>
@@ -23,12 +23,12 @@
     <t>uri</t>
   </si>
   <si>
-    <t>hyperlink</t>
-  </si>
-  <si>
     <t>external_uri</t>
   </si>
   <si>
+    <t>external_vocab_scheme</t>
+  </si>
+  <si>
     <t>Modeled structure</t>
   </si>
   <si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>http://inspire.ec.europa.eu/codelist/FoldProfileTypeValue/anticline</t>
+  </si>
+  <si>
+    <t>inspire</t>
   </si>
   <si>
     <t>modelled antiform</t>
@@ -4675,5360 +4678,5372 @@
       <c r="G28" t="s">
         <v>60</v>
       </c>
+      <c r="H28" t="s">
+        <v>61</v>
+      </c>
       <c r="I28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="D29" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29" t="s">
+        <v>65</v>
+      </c>
+      <c r="I29" t="s">
         <v>62</v>
-      </c>
-      <c r="G29" t="s">
-        <v>63</v>
-      </c>
-      <c r="I29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="D30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="H30" t="s">
+        <v>68</v>
       </c>
       <c r="I30" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="D31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="H31" t="s">
+        <v>71</v>
       </c>
       <c r="I31" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="C32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="C33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="D34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="D35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="C38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="C39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="C40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="C41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="C43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="C44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="C45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="C46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="C47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="C48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="C49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="C50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G50" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="C51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="C52" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="C53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="C54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="C55" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="C56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="C57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="C58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="C59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G59" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="C60" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="C61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="C62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="C63" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G63" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="C64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="C65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="C66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="C67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="C68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="C69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G69" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="C70" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G70" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="C71" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G71" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="C72" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G72" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="C73" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G73" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="C74" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G74" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="C75" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G75" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="C76" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G76" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="C77" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G77" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="C78" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="C79" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G79" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="C80" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="C81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G81" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="C82" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G82" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="C83" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G83" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="C84" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G84" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="C85" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="C86" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G86" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="C87" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G87" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="C88" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G88" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="C89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G89" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="C90" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G90" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="C91" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G91" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="C92" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G92" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="C93" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="C94" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G94" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="C95" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G95" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="C96" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G96" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="C97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="C98" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G98" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="C99" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G99" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="C100" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="C101" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="C102" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="C103" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G103" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="C104" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G104" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="C105" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G105" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="C106" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G106" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="C107" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G107" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="C108" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G108" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="C109" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G109" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="C110" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G110" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="B111" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="C112" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G112" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="C113" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G113" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="C114" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G114" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="C115" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G115" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="C116" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G116" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="C117" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G117" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="C118" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G118" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="C119" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G119" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="C120" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="C121" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G121" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="C122" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G122" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="C123" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G123" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="B124" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G124" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="C125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G125" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="C126" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G126" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="C127" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G127" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="C128" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G128" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="C129" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G129" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="C130" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G130" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="C131" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="C132" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="C133" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G133" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="C134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G134" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="C135" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G135" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="C136" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G136" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="C137" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G137" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="C138" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G138" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="C139" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G139" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="C140" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G140" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="C141" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="C142" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G142" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="C143" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G143" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="C144" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G144" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="C145" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G145" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="C146" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G146" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="C147" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G147" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="C148" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G148" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="C149" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G149" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="C150" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G150" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="C151" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G151" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="C152" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G152" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="C153" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G153" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="C154" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G154" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="C155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G155" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="C156" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G156" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="C157" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G157" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="C158" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G158" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="C159" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G159" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="C160" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G160" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="C161" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G161" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="C162" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G162" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="C163" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G163" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="C164" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G164" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="C165" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G165" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="C166" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G166" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="C167" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G167" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="C168" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G168" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="C169" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G169" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="C170" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G170" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="B171" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G171" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="C172" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G172" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="C173" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F173" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G173" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="C174" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G174" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="C175" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G175" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="C176" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G176" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="C177" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G177" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="C178" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G178" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="C179" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G179" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="C180" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G180" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="C181" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G181" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="C182" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G182" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="C183" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G183" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="C184" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G184" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="C185" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G185" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="C186" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G186" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="C187" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G187" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="C188" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F188" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G188" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="C189" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G189" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="C190" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G190" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="C191" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G191" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="C192" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G192" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="C193" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G193" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="C194" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G194" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="C195" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G195" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="C196" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G196" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="C197" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G197" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="C198" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G198" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="C199" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G199" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="C200" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G200" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="C201" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G201" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="C202" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G202" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="C203" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G203" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="C204" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G204" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="C205" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G205" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="C206" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G206" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="C207" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G207" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="C208" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G208" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="C209" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G209" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="C210" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G210" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="C211" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G211" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="C212" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G212" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="C213" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G213" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="C214" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G214" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="C215" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G215" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="C216" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G216" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="C217" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G217" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="C218" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G218" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="C219" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G219" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="C220" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G220" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="C221" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G221" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="C222" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G222" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="C223" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G223" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="C224" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G224" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="C225" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G225" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="C226" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G226" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="C227" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G227" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="B228" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F228" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G228" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="C229" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G229" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="C230" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G230" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="C231" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G231" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="C232" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G232" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="C233" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G233" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="C234" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G234" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="C235" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G235" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="C236" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G236" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="C237" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G237" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="B238" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G238" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="C239" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G239" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="C240" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G240" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="C241" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G241" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="C242" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G242" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="C243" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G243" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="C244" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G244" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="C245" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G245" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="C246" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G246" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="C247" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G247" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="C248" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G248" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="C249" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G249" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="C250" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G250" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="B251" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G251" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G252" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="C253" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G253" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="C254" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G254" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="C255" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G255" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="C256" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G256" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="C257" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G257" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="C258" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G258" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="C259" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G259" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="C260" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G260" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="C261" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G261" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="C262" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G262" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="C263" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G263" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="C264" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G264" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="C265" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G265" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="C266" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G266" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="C267" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G267" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="C268" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G268" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="C269" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G269" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="C270" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G270" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="C271" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G271" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="C272" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G272" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="C273" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G273" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="C274" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G274" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="C275" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G275" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="C276" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G276" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="C277" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G277" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="C278" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G278" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="C279" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G279" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="C280" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G280" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="C281" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G281" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="C282" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G282" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="C283" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G283" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="C284" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G284" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="C285" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G285" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="C286" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G286" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="C287" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G287" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="C288" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G288" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="C289" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G289" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="C290" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G290" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="C291" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G291" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="C292" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G292" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="C293" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G293" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="B294" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G294" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="C295" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G295" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="C296" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G296" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="C297" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G297" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="C298" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G298" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="C299" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G299" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="C300" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G300" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="C301" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G301" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="C302" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G302" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="C303" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G303" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="C304" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G304" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="C305" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G305" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="C306" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G306" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="C307" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G307" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="C308" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G308" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="309" spans="1:9">
       <c r="C309" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G309" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="C310" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G310" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="C311" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G311" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="C312" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G312" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="C313" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G313" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="C314" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G314" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="C315" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G315" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="C316" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G316" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="C317" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G317" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="C318" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G318" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="C319" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G319" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="C320" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G320" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="C321" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G321" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="C322" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G322" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="C323" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G323" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="C324" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G324" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="C325" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G325" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="C326" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G326" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="C327" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G327" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="328" spans="1:9">
       <c r="C328" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G328" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="329" spans="1:9">
       <c r="B329" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G329" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="C330" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G330" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="C331" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G331" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="332" spans="1:9">
       <c r="C332" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G332" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="333" spans="1:9">
       <c r="C333" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G333" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="334" spans="1:9">
       <c r="C334" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G334" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="335" spans="1:9">
       <c r="C335" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G335" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="336" spans="1:9">
       <c r="C336" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G336" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="337" spans="1:9">
       <c r="C337" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G337" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="338" spans="1:9">
       <c r="C338" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G338" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="339" spans="1:9">
       <c r="C339" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G339" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="340" spans="1:9">
       <c r="C340" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G340" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="341" spans="1:9">
       <c r="B341" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G341" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="342" spans="1:9">
       <c r="C342" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G342" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="343" spans="1:9">
       <c r="C343" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G343" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="344" spans="1:9">
       <c r="C344" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G344" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="345" spans="1:9">
       <c r="C345" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G345" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="346" spans="1:9">
       <c r="C346" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G346" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="347" spans="1:9">
       <c r="C347" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G347" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="348" spans="1:9">
       <c r="C348" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G348" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="349" spans="1:9">
       <c r="C349" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G349" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="350" spans="1:9">
       <c r="C350" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G350" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="351" spans="1:9">
       <c r="C351" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G351" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="352" spans="1:9">
       <c r="C352" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G352" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="353" spans="1:9">
       <c r="C353" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G353" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="354" spans="1:9">
       <c r="C354" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G354" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="355" spans="1:9">
       <c r="C355" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G355" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="356" spans="1:9">
       <c r="C356" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G356" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="357" spans="1:9">
       <c r="C357" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G357" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="358" spans="1:9">
       <c r="C358" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G358" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="359" spans="1:9">
       <c r="C359" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G359" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="360" spans="1:9">
       <c r="C360" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G360" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="361" spans="1:9">
       <c r="C361" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G361" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="362" spans="1:9">
       <c r="C362" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G362" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="363" spans="1:9">
       <c r="C363" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G363" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="364" spans="1:9">
       <c r="C364" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G364" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="365" spans="1:9">
       <c r="C365" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G365" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="366" spans="1:9">
       <c r="C366" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G366" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="367" spans="1:9">
       <c r="C367" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G367" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="368" spans="1:9">
       <c r="C368" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G368" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="369" spans="1:9">
       <c r="C369" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G369" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="370" spans="1:9">
       <c r="C370" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G370" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="371" spans="1:9">
       <c r="C371" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G371" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="372" spans="1:9">
       <c r="C372" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G372" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="373" spans="1:9">
       <c r="C373" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G373" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="374" spans="1:9">
       <c r="C374" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G374" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="375" spans="1:9">
       <c r="C375" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G375" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="376" spans="1:9">
       <c r="C376" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G376" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="377" spans="1:9">
       <c r="C377" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G377" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="378" spans="1:9">
       <c r="C378" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G378" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="379" spans="1:9">
       <c r="C379" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G379" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="380" spans="1:9">
       <c r="C380" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G380" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="381" spans="1:9">
       <c r="C381" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G381" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="382" spans="1:9">
       <c r="C382" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G382" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="383" spans="1:9">
       <c r="D383" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G383" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="384" spans="1:9">
       <c r="D384" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G384" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="385" spans="1:9">
       <c r="D385" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G385" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="386" spans="1:9">
       <c r="D386" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G386" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="387" spans="1:9">
       <c r="D387" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G387" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="388" spans="1:9">
       <c r="D388" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G388" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="389" spans="1:9">
       <c r="D389" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G389" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="390" spans="1:9">
       <c r="B390" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G390" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="391" spans="1:9">
       <c r="C391" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G391" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="392" spans="1:9">
       <c r="C392" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G392" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="393" spans="1:9">
       <c r="C393" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G393" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="394" spans="1:9">
       <c r="C394" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G394" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="395" spans="1:9">
       <c r="C395" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G395" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="396" spans="1:9">
       <c r="C396" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="G396" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="397" spans="1:9">
       <c r="C397" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G397" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="398" spans="1:9">
       <c r="C398" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G398" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="399" spans="1:9">
       <c r="C399" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G399" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="400" spans="1:9">
       <c r="C400" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G400" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="401" spans="1:9">
       <c r="C401" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G401" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="G402" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="403" spans="1:9">
       <c r="B403" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F403" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="G403" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="404" spans="1:9">
       <c r="C404" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F404" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G404" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="405" spans="1:9">
       <c r="D405" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G405" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="406" spans="1:9">
       <c r="E406" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G406" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="407" spans="1:9">
       <c r="E407" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="G407" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="408" spans="1:9">
       <c r="D408" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G408" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="409" spans="1:9">
       <c r="E409" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F409" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G409" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="410" spans="1:9">
       <c r="E410" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F410" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G410" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="411" spans="1:9">
       <c r="D411" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="G411" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="412" spans="1:9">
       <c r="D412" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G412" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="413" spans="1:9">
       <c r="D413" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G413" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="414" spans="1:9">
       <c r="E414" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G414" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="415" spans="1:9">
       <c r="E415" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G415" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="416" spans="1:9">
       <c r="D416" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G416" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="417" spans="1:9">
       <c r="E417" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G417" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="418" spans="1:9">
       <c r="E418" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G418" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="419" spans="1:9">
       <c r="D419" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F419" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G419" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="420" spans="1:9">
       <c r="C420" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G420" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="421" spans="1:9">
       <c r="D421" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G421" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="422" spans="1:9">
       <c r="D422" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G422" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="423" spans="1:9">
       <c r="C423" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="G423" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="424" spans="1:9">
       <c r="D424" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="G424" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="425" spans="1:9">
       <c r="D425" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G425" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="426" spans="1:9">
       <c r="D426" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G426" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="427" spans="1:9">
       <c r="E427" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G427" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="428" spans="1:9">
       <c r="E428" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G428" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="429" spans="1:9">
       <c r="D429" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G429" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="430" spans="1:9">
       <c r="E430" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G430" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="431" spans="1:9">
       <c r="E431" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G431" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="432" spans="1:9">
       <c r="C432" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F432" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G432" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="433" spans="1:9">
       <c r="D433" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G433" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="434" spans="1:9">
       <c r="E434" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G434" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="435" spans="1:9">
       <c r="E435" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="G435" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="436" spans="1:9">
       <c r="D436" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G436" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="437" spans="1:9">
       <c r="E437" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G437" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="438" spans="1:9">
       <c r="E438" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G438" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="439" spans="1:9">
       <c r="D439" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G439" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="440" spans="1:9">
       <c r="D440" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G440" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="441" spans="1:9">
       <c r="D441" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="G441" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="442" spans="1:9">
       <c r="D442" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G442" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="443" spans="1:9">
       <c r="D443" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G443" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="444" spans="1:9">
       <c r="D444" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G444" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="445" spans="1:9">
       <c r="D445" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F445" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G445" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="446" spans="1:9">
       <c r="C446" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G446" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="447" spans="1:9">
       <c r="D447" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="G447" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="448" spans="1:9">
       <c r="D448" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G448" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="449" spans="1:9">
       <c r="B449" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F449" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G449" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="450" spans="1:9">
       <c r="C450" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G450" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="451" spans="1:9">
       <c r="D451" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F451" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G451" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="452" spans="1:9">
       <c r="C452" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G452" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="453" spans="1:9">
       <c r="D453" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G453" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="454" spans="1:9">
       <c r="D454" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G454" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="455" spans="1:9">
       <c r="D455" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G455" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="456" spans="1:9">
       <c r="D456" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G456" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="457" spans="1:9">
       <c r="C457" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G457" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="458" spans="1:9">
       <c r="D458" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F458" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G458" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="459" spans="1:9">
       <c r="D459" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G459" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="460" spans="1:9">
       <c r="D460" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G460" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="461" spans="1:9">
       <c r="D461" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G461" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="462" spans="1:9">
       <c r="C462" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G462" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="463" spans="1:9">
       <c r="D463" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G463" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="464" spans="1:9">
       <c r="D464" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G464" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="465" spans="1:9">
       <c r="D465" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G465" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="466" spans="1:9">
       <c r="D466" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="G466" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="467" spans="1:9">
       <c r="C467" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G467" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="468" spans="1:9">
       <c r="D468" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="G468" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="469" spans="1:9">
       <c r="D469" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="G469" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="470" spans="1:9">
       <c r="D470" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G470" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="471" spans="1:9">
       <c r="D471" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="G471" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="472" spans="1:9">
       <c r="C472" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F472" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G472" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="473" spans="1:9">
       <c r="D473" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G473" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="474" spans="1:9">
       <c r="D474" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F474" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="G474" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="475" spans="1:9">
       <c r="A475" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="G475" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="476" spans="1:9">
       <c r="B476" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F476" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G476" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="477" spans="1:9">
       <c r="C477" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F477" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G477" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="478" spans="1:9">
       <c r="D478" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F478" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G478" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="479" spans="1:9">
       <c r="D479" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F479" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="G479" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="480" spans="1:9">
       <c r="C480" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F480" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="G480" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="481" spans="1:9">
       <c r="C481" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G481" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="482" spans="1:9">
       <c r="C482" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F482" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G482" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="483" spans="1:9">
       <c r="C483" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F483" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="G483" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="484" spans="1:9">
       <c r="D484" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="G484" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="485" spans="1:9">
       <c r="D485" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G485" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="486" spans="1:9">
       <c r="C486" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G486" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="487" spans="1:9">
       <c r="C487" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G487" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="488" spans="1:9">
       <c r="C488" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G488" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="489" spans="1:9">
       <c r="C489" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F489" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="G489" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="490" spans="1:9">
       <c r="C490" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G490" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="491" spans="1:9">
       <c r="C491" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G491" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="492" spans="1:9">
       <c r="C492" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G492" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="493" spans="1:9">
       <c r="C493" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F493" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G493" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="494" spans="1:9">
       <c r="B494" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G494" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="495" spans="1:9">
       <c r="C495" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="G495" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="496" spans="1:9">
       <c r="C496" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F496" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="G496" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="497" spans="1:9">
       <c r="D497" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F497" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="G497" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="498" spans="1:9">
       <c r="D498" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F498" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="G498" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="499" spans="1:9">
       <c r="D499" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F499" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G499" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="500" spans="1:9">
       <c r="D500" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F500" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G500" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="501" spans="1:9">
       <c r="C501" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G501" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="502" spans="1:9">
       <c r="D502" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G502" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="503" spans="1:9">
       <c r="D503" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G503" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="504" spans="1:9">
       <c r="B504" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F504" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G504" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="505" spans="1:9">
       <c r="C505" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F505" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="G505" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="506" spans="1:9">
       <c r="C506" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F506" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="G506" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="507" spans="1:9">
       <c r="C507" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F507" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G507" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="508" spans="1:9">
       <c r="B508" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G508" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="509" spans="1:9">
       <c r="C509" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="G509" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="510" spans="1:9">
       <c r="C510" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G510" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="511" spans="1:9">
       <c r="C511" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F511" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="G511" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="512" spans="1:9">
       <c r="B512" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="G512" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="513" spans="1:9">
       <c r="C513" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F513" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G513" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="514" spans="1:9">
       <c r="C514" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G514" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="515" spans="1:9">
       <c r="C515" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G515" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="516" spans="1:9">
       <c r="C516" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F516" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G516" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="517" spans="1:9">
       <c r="B517" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G517" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="518" spans="1:9">
       <c r="C518" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G518" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="519" spans="1:9">
       <c r="C519" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="G519" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="520" spans="1:9">
       <c r="A520" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G520" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="521" spans="1:9">
       <c r="B521" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G521" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="522" spans="1:9">
       <c r="C522" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F522" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G522" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="523" spans="1:9">
       <c r="C523" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="G523" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="524" spans="1:9">
       <c r="C524" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F524" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G524" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="525" spans="1:9">
       <c r="C525" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G525" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="526" spans="1:9">
       <c r="C526" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G526" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="527" spans="1:9">
       <c r="C527" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="G527" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="528" spans="1:9">
       <c r="C528" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G528" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="529" spans="1:9">
       <c r="D529" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F529" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G529" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="530" spans="1:9">
       <c r="C530" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G530" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="531" spans="1:9">
       <c r="B531" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F531" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="G531" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="532" spans="1:9">
       <c r="C532" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F532" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G532" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="533" spans="1:9">
       <c r="D533" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="G533" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="534" spans="1:9">
       <c r="D534" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G534" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="535" spans="1:9">
       <c r="D535" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G535" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="536" spans="1:9">
       <c r="D536" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F536" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G536" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="537" spans="1:9">
       <c r="D537" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F537" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G537" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="538" spans="1:9">
       <c r="C538" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F538" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G538" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="539" spans="1:9">
       <c r="C539" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G539" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="540" spans="1:9">
       <c r="C540" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F540" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G540" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="541" spans="1:9">
       <c r="C541" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="G541" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="542" spans="1:9">
       <c r="C542" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G542" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="543" spans="1:9">
       <c r="C543" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="G543" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="544" spans="1:9">
       <c r="C544" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G544" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="545" spans="1:9">
       <c r="C545" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G545" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="546" spans="1:9">
       <c r="B546" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G546" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="547" spans="1:9">
       <c r="C547" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G547" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="548" spans="1:9">
       <c r="B548" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F548" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G548" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="549" spans="1:9">
       <c r="C549" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G549" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="550" spans="1:9">
       <c r="C550" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G550" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="551" spans="1:9">
       <c r="C551" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F551" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G551" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="552" spans="1:9">
       <c r="B552" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G552" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="553" spans="1:9">
       <c r="B553" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F553" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="G553" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="554" spans="1:9">
       <c r="B554" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="G554" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="555" spans="1:9">
       <c r="B555" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G555" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="556" spans="1:9">
       <c r="C556" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F556" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="G556" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="557" spans="1:9">
       <c r="C557" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G557" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="558" spans="1:9">
       <c r="C558" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="G558" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="559" spans="1:9">
       <c r="C559" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G559" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="560" spans="1:9">
       <c r="C560" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G560" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="561" spans="1:9">
       <c r="C561" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="G561" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="562" spans="1:9">
       <c r="C562" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G562" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="563" spans="1:9">
       <c r="C563" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="G563" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="564" spans="1:9">
       <c r="C564" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="G564" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="565" spans="1:9">
       <c r="C565" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="G565" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="566" spans="1:9">
       <c r="C566" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="G566" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="567" spans="1:9">
       <c r="C567" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F567" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G567" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="568" spans="1:9">
       <c r="B568" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G568" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="569" spans="1:9">
       <c r="C569" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F569" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G569" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="570" spans="1:9">
       <c r="C570" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="F570" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G570" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="571" spans="1:9">
       <c r="C571" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G571" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="572" spans="1:9">
       <c r="C572" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="G572" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="573" spans="1:9">
       <c r="C573" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="G573" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="574" spans="1:9">
       <c r="B574" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="F574" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="G574" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="575" spans="1:9">
       <c r="C575" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F575" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="G575" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="576" spans="1:9">
       <c r="C576" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F576" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="G576" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="577" spans="1:9">
       <c r="C577" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F577" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G577" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="578" spans="1:9">
       <c r="B578" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="G578" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="579" spans="1:9">
       <c r="B579" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G579" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="580" spans="1:9">
       <c r="C580" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="G580" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="581" spans="1:9">
       <c r="C581" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="G581" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="582" spans="1:9">
       <c r="B582" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G582" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="583" spans="1:9">
       <c r="C583" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="G583" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="584" spans="1:9">
       <c r="C584" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G584" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="585" spans="1:9">
       <c r="C585" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="G585" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="586" spans="1:9">
       <c r="C586" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F586" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G586" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="587" spans="1:9">
       <c r="B587" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="G587" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="588" spans="1:9">
       <c r="C588" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="G588" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="589" spans="1:9">
       <c r="C589" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="G589" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="590" spans="1:9">
       <c r="B590" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="G590" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="591" spans="1:9">
       <c r="B591" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="G591" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="592" spans="1:9">
       <c r="C592" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="G592" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="593" spans="1:9">
       <c r="C593" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G593" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="594" spans="1:9">
       <c r="C594" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="G594" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="595" spans="1:9">
       <c r="B595" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="F595" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="G595" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="596" spans="1:9">
       <c r="C596" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G596" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="597" spans="1:9">
       <c r="C597" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G597" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="598" spans="1:9">
       <c r="B598" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="G598" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="599" spans="1:9">
       <c r="B599" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="G599" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="600" spans="1:9">
       <c r="A600" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="G600" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="601" spans="1:9">
       <c r="B601" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F601" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="G601" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="602" spans="1:9">
       <c r="C602" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F602" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G602" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="603" spans="1:9">
       <c r="C603" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="F603" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G603" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="604" spans="1:9">
       <c r="C604" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="F604" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G604" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="605" spans="1:9">
       <c r="D605" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="F605" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="G605" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="606" spans="1:9">
       <c r="D606" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="F606" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="G606" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="607" spans="1:9">
       <c r="D607" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="F607" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="G607" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="608" spans="1:9">
       <c r="B608" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="F608" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="G608" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="609" spans="1:9">
       <c r="C609" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F609" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G609" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="610" spans="1:9">
       <c r="C610" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F610" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="G610" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="611" spans="1:9">
       <c r="C611" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F611" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="G611" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="612" spans="1:9">
       <c r="C612" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="F612" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="G612" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="613" spans="1:9">
       <c r="C613" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="F613" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="G613" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="614" spans="1:9">
       <c r="C614" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="F614" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G614" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="615" spans="1:9">
       <c r="C615" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="F615" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="G615" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="616" spans="1:9">
       <c r="C616" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F616" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="G616" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="617" spans="1:9">
       <c r="B617" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="G617" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="618" spans="1:9">
       <c r="B618" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="G618" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="619" spans="1:9">
       <c r="B619" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="G619" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="620" spans="1:9">
       <c r="B620" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G620" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="621" spans="1:9">
       <c r="B621" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="G621" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="622" spans="1:9">
       <c r="B622" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G622" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="623" spans="1:9">
       <c r="B623" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G623" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="624" spans="1:9">
       <c r="B624" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G624" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="625" spans="1:9">
       <c r="B625" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="G625" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="626" spans="1:9">
       <c r="B626" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G626" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="627" spans="1:9">
       <c r="B627" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="G627" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="628" spans="1:9">
       <c r="B628" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="G628" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="629" spans="1:9">
       <c r="B629" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="G629" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="630" spans="1:9">
       <c r="B630" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="G630" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="631" spans="1:9">
       <c r="B631" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="G631" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="632" spans="1:9">
       <c r="B632" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G632" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="633" spans="1:9">
       <c r="B633" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G633" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="634" spans="1:9">
       <c r="B634" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G634" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="635" spans="1:9">
       <c r="B635" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G635" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="636" spans="1:9">
       <c r="B636" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="G636" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="637" spans="1:9">
       <c r="B637" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="G637" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="638" spans="1:9">
       <c r="B638" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="G638" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="639" spans="1:9">
       <c r="B639" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="G639" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="640" spans="1:9">
       <c r="B640" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="G640" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="641" spans="1:9">
       <c r="B641" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="G641" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="642" spans="1:9">
       <c r="B642" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="G642" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="643" spans="1:9">
       <c r="B643" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="G643" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="644" spans="1:9">
       <c r="B644" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="G644" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="645" spans="1:9">
       <c r="B645" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="F645" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="G645" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="646" spans="1:9">
       <c r="B646" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="G646" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="647" spans="1:9">
       <c r="B647" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="G647" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="648" spans="1:9">
       <c r="B648" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="G648" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="649" spans="1:9">
       <c r="B649" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="G649" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="650" spans="1:9">
       <c r="B650" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="G650" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="651" spans="1:9">
       <c r="B651" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="G651" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="652" spans="1:9">
       <c r="B652" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="G652" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="653" spans="1:9">
       <c r="B653" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="G653" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="654" spans="1:9">
       <c r="B654" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="G654" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="655" spans="1:9">
       <c r="B655" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G655" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="656" spans="1:9">
       <c r="B656" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="G656" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="657" spans="1:9">
       <c r="B657" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="G657" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="658" spans="1:9">
       <c r="B658" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="G658" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="659" spans="1:9">
       <c r="B659" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="G659" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="660" spans="1:9">
       <c r="B660" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="G660" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="661" spans="1:9">
       <c r="B661" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="G661" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="662" spans="1:9">
       <c r="B662" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="G662" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="663" spans="1:9">
       <c r="B663" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="G663" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="664" spans="1:9">
       <c r="B664" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="G664" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="665" spans="1:9">
       <c r="B665" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="G665" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="666" spans="1:9">
       <c r="B666" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="G666" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="667" spans="1:9">
       <c r="B667" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="G667" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
   </sheetData>
